--- a/routing_config.xlsx
+++ b/routing_config.xlsx
@@ -423,14 +423,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -463,12 +463,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ohjelmisto, tietojärjestelmä, ICT, digitaalinen, sovellus, järjestelmä, robotiikka, tekoäly, AI</t>
+          <t>ohjelmisto, tietojärjestelm, ICT, digitaali, sovellus, järjestelm, robotiikka, tekoäly, AI, tiedonhallin, pilvipalvelu, SaaS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IT Consulting</t>
+          <t>IT &amp; Software</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -478,24 +478,24 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>valoraami@gmail.com</t>
+          <t>ville.pajala@cgi.com</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Software and IT systems</t>
+          <t>Software, IT systems, cloud, AI, data platforms</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>rakennus, urakka, perusparannus, rakentaminen, projektinjohto, saneeraus</t>
+          <t>tietoturva, kyberturvallisuus, tietosuoja, identiteetti, pääsynhallin, SIEM, SOC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -505,24 +505,24 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>valoraami@gmail.com</t>
+          <t>ville.pajala@cgi.com</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Building and renovation projects</t>
+          <t>Cybersecurity, identity management, monitoring</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>siivous, laitoshuolto, puhdistus, hygienia, catering, ravintola</t>
+          <t>konsultoin, konsultti, asiantuntija, selvitys, tutkimus, strategia, kehittäminen, muutosjohtaminen</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Facility Services</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -532,24 +532,24 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>valoraami@gmail.com</t>
+          <t>ville.pajala@cgi.com</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cleaning and facility management</t>
+          <t>IT consulting, business consulting, strategy</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>konsultti, asiantuntija, suunnittelu, selvitys, tutkimus</t>
+          <t>terveys, sosiaali, hoito, kuntoutu, potilas, asiakas, hyvinvointialue, SOTE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Health &amp; Social</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -559,24 +559,24 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>valoraami@gmail.com</t>
+          <t>ville.pajala@cgi.com</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Professional consulting services</t>
+          <t>Healthcare IT, patient systems, wellbeing regions</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>terveys, sosiaali, hoito, kuntoutus, lääk, hammas, apuväline</t>
+          <t>palkk, palkan, henkilöstö, HR, työvuoro, työajanseuran, rekrytoin</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Health &amp; Social</t>
+          <t>HR &amp; Payroll</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -586,24 +586,24 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>valoraami@gmail.com</t>
+          <t>ville.pajala@cgi.com</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Healthcare and social services</t>
+          <t>HR systems, payroll, workforce scheduling</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>liikenne, infra, katu, silta, vesi, viemäri, sähkö, energia</t>
+          <t>talous, kirjanpito, laskutus, maksuliiken, ERP, toiminnanohjaus, hankin</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Financial Systems</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -613,24 +613,24 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>valoraami@gmail.com</t>
+          <t>ville.pajala@cgi.com</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Infrastructure and utilities</t>
+          <t>ERP, financial management, procurement systems</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>koulutus, opetus, varhaiskasvatus, päiväkoti, koulu</t>
+          <t>integraatio, rajapinta, API-rajapinta, tiedonsiirto, konversio, migraatio</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -640,37 +640,91 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>valoraami@gmail.com</t>
+          <t>ville.pajala@cgi.com</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Education and training</t>
+          <t>System integration, APIs, data migration</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>koulut, opetus, oppiminen, opiskelij, oppilas, varhaiskasvatus</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Test User</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ville.pajala@cgi.com</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Education IT systems, learning platforms</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>kartta, paikkatieto, GIS, rekisteri, maankäyttö, kaavoitus, kiinteistö</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Geospatial &amp; Registry</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Test User</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ville.pajala@cgi.com</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Municipal registries, GIS, land use systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>*</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Test User</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>valoraami@gmail.com</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Test User</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ville.pajala@cgi.com</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>Catch-all for unmatched tenders</t>
         </is>
